--- a/ZonasEscolares/excels/UCAYALI-CORONEL_PORTILLO-CALLERIA.xlsx
+++ b/ZonasEscolares/excels/UCAYALI-CORONEL_PORTILLO-CALLERIA.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -555,7 +555,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3467,7 +3467,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/UCAYALI-CORONEL_PORTILLO-CALLERIA.xlsx
+++ b/ZonasEscolares/excels/UCAYALI-CORONEL_PORTILLO-CALLERIA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>64140</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-8.602410000000003</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-74.31007</v>
-      </c>
-      <c r="I2" t="n">
-        <v>221</v>
-      </c>
-      <c r="J2" t="n">
-        <v>11</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-8.602410000000003</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-74.31007</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>232 NIÑO JESUS</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-8.380687</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-74.52893</v>
-      </c>
-      <c r="I3" t="n">
-        <v>775</v>
-      </c>
-      <c r="J3" t="n">
-        <v>33</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-8.380687</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-74.52893</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>775</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>235 SANTA ROSA</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-8.387554</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-74.534025</v>
-      </c>
-      <c r="I4" t="n">
-        <v>787</v>
-      </c>
-      <c r="J4" t="n">
-        <v>30</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-8.387554</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-74.534025</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>787</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>241</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-8.390618</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-74.541539</v>
-      </c>
-      <c r="I5" t="n">
-        <v>248</v>
-      </c>
-      <c r="J5" t="n">
-        <v>12</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-8.390618</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-74.541539</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>242 DIVINO MAESTRO</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-8.381145999999999</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-74.54642</v>
-      </c>
-      <c r="I6" t="n">
-        <v>540</v>
-      </c>
-      <c r="J6" t="n">
-        <v>23</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-8.381146</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-74.54642</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>261 VICTORIA BARCIA BONIFATI</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-8.377184</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-74.537679</v>
-      </c>
-      <c r="I7" t="n">
-        <v>803</v>
-      </c>
-      <c r="J7" t="n">
-        <v>35</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-8.377184</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-74.537679</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>803</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>268</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-8.388225</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-74.549952</v>
-      </c>
-      <c r="I8" t="n">
-        <v>202</v>
-      </c>
-      <c r="J8" t="n">
-        <v>10</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-8.388225</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-74.549952</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>269 ELVIRA GARCIA Y GARCIA</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-8.373144</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-74.551557</v>
-      </c>
-      <c r="I9" t="n">
-        <v>342</v>
-      </c>
-      <c r="J9" t="n">
-        <v>14</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-8.373144</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-74.551557</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>283 JUANA ALARCO DE DAMMERT</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-8.373602999999999</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-74.52995300000001</v>
-      </c>
-      <c r="I10" t="n">
-        <v>343</v>
-      </c>
-      <c r="J10" t="n">
-        <v>16</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-8.373603</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-74.529953</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>311 SOR ANGELA CATELLI CATELLI</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-8.384315000000003</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-74.54246500000001</v>
-      </c>
-      <c r="I11" t="n">
-        <v>347</v>
-      </c>
-      <c r="J11" t="n">
-        <v>13</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-8.384315000000003</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-74.542465</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>435</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-8.410572999999999</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-74.58510200000001</v>
-      </c>
-      <c r="I12" t="n">
-        <v>243</v>
-      </c>
-      <c r="J12" t="n">
-        <v>10</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-8.410573</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-74.585102</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>479 / 64001 / DANIEL ALCIDES CARRION</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-8.386652</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-74.5551</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1363</v>
-      </c>
-      <c r="J13" t="n">
-        <v>70</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-8.386652</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-74.5551</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>64004 MARGARITA A. AGUILAR A. / MARGARITA AURORA AGUILAR</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-8.380832</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-74.543227</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1101</v>
-      </c>
-      <c r="J14" t="n">
-        <v>52</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-8.380832</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-74.543227</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>64005 FRANCISCO BOLOGNESI</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-8.393302</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-74.541732</v>
-      </c>
-      <c r="I15" t="n">
-        <v>803</v>
-      </c>
-      <c r="J15" t="n">
-        <v>40</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-8.393302</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-74.541732</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>803</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>64006 JORGE CHAVEZ / JORGE CHAVEZ</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-8.384460000000002</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-74.54182900000001</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1708</v>
-      </c>
-      <c r="J16" t="n">
-        <v>80</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-8.384460000000002</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-74.541829</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1708</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>64007 SANTA ROSA</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-8.389818</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-74.530777</v>
-      </c>
-      <c r="I17" t="n">
-        <v>953</v>
-      </c>
-      <c r="J17" t="n">
-        <v>34</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-8.389818</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-74.530777</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>64008 EL ORIENTE</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-8.378125000000002</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-74.546306</v>
-      </c>
-      <c r="I18" t="n">
-        <v>307</v>
-      </c>
-      <c r="J18" t="n">
-        <v>15</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-8.378125000000002</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-74.546306</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>64011 SOR ANNETA DE JESUS</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-8.38029</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-74.52855</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1574</v>
-      </c>
-      <c r="J19" t="n">
-        <v>58</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-8.38029</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-74.52855</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1574</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>64012 MIGUEL GRAU</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-8.378917</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-74.53428099999999</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1375</v>
-      </c>
-      <c r="J20" t="n">
-        <v>48</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-8.378917</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-74.534281</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1375</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>EL ARENAL</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-8.374447999999999</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-74.53518099999999</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1910</v>
-      </c>
-      <c r="J21" t="n">
-        <v>87</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-8.374448</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-74.535181</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1910</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>64017</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-8.374641</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-74.530629</v>
-      </c>
-      <c r="I22" t="n">
-        <v>529</v>
-      </c>
-      <c r="J22" t="n">
-        <v>23</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-8.374641</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-74.530629</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>529</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>ABNER ALBERTO MONROY CACHAY</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-8.370202000000003</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-74.53621</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1289</v>
-      </c>
-      <c r="J23" t="n">
-        <v>51</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-8.370202000000003</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-74.53621</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1289</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>474 / 64020 LUIS ALBERTO SANCHEZ SANCHEZ</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-8.373753000000002</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-74.551089</v>
-      </c>
-      <c r="I24" t="n">
-        <v>817</v>
-      </c>
-      <c r="J24" t="n">
-        <v>36</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-8.373753000000002</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-74.551089</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>817</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>64023</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-8.375804</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-74.543581</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1258</v>
-      </c>
-      <c r="J25" t="n">
-        <v>58</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-8.375804</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-74.543581</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1258</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>346 ROSA MERINO / 64024</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-8.381145</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-74.536817</v>
-      </c>
-      <c r="I26" t="n">
-        <v>860</v>
-      </c>
-      <c r="J26" t="n">
-        <v>39</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-8.381145</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-74.536817</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>64035 AGROPECUARIO / COAR UCAYALI</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-8.391996000000002</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-74.549076</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1616</v>
-      </c>
-      <c r="J27" t="n">
-        <v>76</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-8.391996000000002</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-74.549076</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1616</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>64036</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-8.393560000000003</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-74.5373</v>
-      </c>
-      <c r="I28" t="n">
-        <v>571</v>
-      </c>
-      <c r="J28" t="n">
-        <v>26</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-8.393560000000003</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-74.5373</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>64058 VICTOR MALDONADO BEGAZO / CRNL. VICTOR M. MALDONADO BEGAZO</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-8.39533</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-74.58996</v>
-      </c>
-      <c r="I29" t="n">
-        <v>2193</v>
-      </c>
-      <c r="J29" t="n">
-        <v>89</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-8.39533</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-74.58996</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2193</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>64359 JOSE GALVEZ EGUSQUIZA</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-8.36726</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-74.541893</v>
-      </c>
-      <c r="I30" t="n">
-        <v>542</v>
-      </c>
-      <c r="J30" t="n">
-        <v>28</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-8.36726</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-74.541893</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>542</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>64803</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-8.4116</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-74.5872</v>
-      </c>
-      <c r="I31" t="n">
-        <v>1378</v>
-      </c>
-      <c r="J31" t="n">
-        <v>61</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-8.4116</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-74.5872</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1378</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>64871-B</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-8.361969999999999</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-74.53072</v>
-      </c>
-      <c r="I32" t="n">
-        <v>204</v>
-      </c>
-      <c r="J32" t="n">
-        <v>10</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-8.36197</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-74.53072</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>65297</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-8.393483</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-74.567212</v>
-      </c>
-      <c r="I33" t="n">
-        <v>395</v>
-      </c>
-      <c r="J33" t="n">
-        <v>22</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-8.393483</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-74.567212</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>65001 CORONEL PEDRO PORTILLO</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-8.386566</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-74.53574999999999</v>
-      </c>
-      <c r="I34" t="n">
-        <v>2579</v>
-      </c>
-      <c r="J34" t="n">
-        <v>102</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-8.386566</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-74.53575</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2579</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>65002 AURISTELA DAVILA ZEVALLOS</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-8.379614</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-74.53924499999999</v>
-      </c>
-      <c r="I35" t="n">
-        <v>1942</v>
-      </c>
-      <c r="J35" t="n">
-        <v>70</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-8.379614</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-74.539245</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1942</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>65003</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-8.3818</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-74.5311</v>
-      </c>
-      <c r="I36" t="n">
-        <v>1749</v>
-      </c>
-      <c r="J36" t="n">
-        <v>67</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-8.3818</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-74.5311</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1749</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>65012 WILLIAN DYER AMPUDIA</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-8.394486000000002</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-74.57143600000001</v>
-      </c>
-      <c r="I37" t="n">
-        <v>1087</v>
-      </c>
-      <c r="J37" t="n">
-        <v>45</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-8.394486000000002</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-74.571436</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1087</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>LA INMACULADA</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-8.378601</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-74.53164099999999</v>
-      </c>
-      <c r="I38" t="n">
-        <v>1912</v>
-      </c>
-      <c r="J38" t="n">
-        <v>98</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-8.378601</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-74.531641</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1912</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>COMERCIO 64</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-8.376640999999999</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-74.53735</v>
-      </c>
-      <c r="I39" t="n">
-        <v>2246</v>
-      </c>
-      <c r="J39" t="n">
-        <v>101</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-8.376641</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-74.53735</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2246</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>NUESTRA SEÑORA DE GUADALUPE</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-8.381727</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-74.52842099999999</v>
-      </c>
-      <c r="I40" t="n">
-        <v>1340</v>
-      </c>
-      <c r="J40" t="n">
-        <v>61</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-8.381727</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-74.528421</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>289</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-8.406682999999999</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-74.56948199999999</v>
-      </c>
-      <c r="I41" t="n">
-        <v>201</v>
-      </c>
-      <c r="J41" t="n">
-        <v>9</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-8.406683</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-74.569482</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>BAUTISTA</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-8.38054</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-74.54519999999999</v>
-      </c>
-      <c r="I42" t="n">
-        <v>204</v>
-      </c>
-      <c r="J42" t="n">
-        <v>19</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-8.38054</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-74.5452</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>UCAYALI</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-8.383784</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-74.52954200000001</v>
-      </c>
-      <c r="I43" t="n">
-        <v>353</v>
-      </c>
-      <c r="J43" t="n">
-        <v>24</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-8.383784</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-74.529542</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>RICARDO PALMA</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-8.380342000000002</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-74.53286199999999</v>
-      </c>
-      <c r="I44" t="n">
-        <v>207</v>
-      </c>
-      <c r="J44" t="n">
-        <v>24</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-8.380342000000002</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-74.532862</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>ANTONIO RAYMONDI</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-8.38297</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-74.552165</v>
-      </c>
-      <c r="I45" t="n">
-        <v>406</v>
-      </c>
-      <c r="J45" t="n">
-        <v>35</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-8.38297</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-74.552165</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>406</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>JOAQUIN CAPELLO</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-8.601812000000002</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-74.310901</v>
-      </c>
-      <c r="I46" t="n">
-        <v>224</v>
-      </c>
-      <c r="J46" t="n">
-        <v>10</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-8.601812000000002</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-74.310901</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>308 NIÑO JESUS DE PRAGA</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-8.37692</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-74.55618</v>
-      </c>
-      <c r="I47" t="n">
-        <v>291</v>
-      </c>
-      <c r="J47" t="n">
-        <v>11</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-8.37692</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-74.55618</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>64693 JOSE OLAYA BALANDRA</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-8.367884</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-74.548317</v>
-      </c>
-      <c r="I48" t="n">
-        <v>709</v>
-      </c>
-      <c r="J48" t="n">
-        <v>20</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-8.367884</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-74.548317</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>709</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>64753 FAUSTINO MALDONADO</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-8.376569</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-74.557574</v>
-      </c>
-      <c r="I49" t="n">
-        <v>2795</v>
-      </c>
-      <c r="J49" t="n">
-        <v>141</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-8.376569</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-74.557574</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2795</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3017,20 +3485,30 @@
           <t>64087</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>-8.310129</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-74.86378499999999</v>
-      </c>
-      <c r="I50" t="n">
-        <v>466</v>
-      </c>
-      <c r="J50" t="n">
-        <v>21</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-8.310129</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-74.863785</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>466</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3069,20 +3547,30 @@
           <t>MARANATHA</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>-8.393969999999999</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-74.56589200000001</v>
-      </c>
-      <c r="I51" t="n">
-        <v>284</v>
-      </c>
-      <c r="J51" t="n">
-        <v>17</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-8.39397</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-74.565892</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3121,20 +3609,30 @@
           <t>HUGO CRUZ DOZA</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>-8.40771</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-74.59058</v>
-      </c>
-      <c r="I52" t="n">
-        <v>1353</v>
-      </c>
-      <c r="J52" t="n">
-        <v>57</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-8.40771</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-74.59058</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3173,20 +3671,30 @@
           <t>65263 / FRANCISCO ODICIO ROMAN</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>-8.414593</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-74.574027</v>
-      </c>
-      <c r="I53" t="n">
-        <v>640</v>
-      </c>
-      <c r="J53" t="n">
-        <v>27</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-8.414593</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-74.574027</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3225,20 +3733,30 @@
           <t>CRISTOBAL DE LOSADA Y PUGA</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>-8.382580000000003</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-74.53570999999999</v>
-      </c>
-      <c r="I54" t="n">
-        <v>279</v>
-      </c>
-      <c r="J54" t="n">
-        <v>16</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-8.382580000000003</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-74.53571</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3277,20 +3795,30 @@
           <t>65271</t>
         </is>
       </c>
-      <c r="G55" t="n">
-        <v>-8.413007</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-74.646582</v>
-      </c>
-      <c r="I55" t="n">
-        <v>750</v>
-      </c>
-      <c r="J55" t="n">
-        <v>32</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-8.413007</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-74.646582</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3329,20 +3857,30 @@
           <t>ADUNI</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>-8.374537</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-74.537192</v>
-      </c>
-      <c r="I56" t="n">
-        <v>594</v>
-      </c>
-      <c r="J56" t="n">
-        <v>33</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-8.374537</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-74.537192</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>594</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3381,20 +3919,30 @@
           <t>DON BOSCO</t>
         </is>
       </c>
-      <c r="G57" t="n">
-        <v>-8.381627</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-74.539068</v>
-      </c>
-      <c r="I57" t="n">
-        <v>299</v>
-      </c>
-      <c r="J57" t="n">
-        <v>21</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-8.381627</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-74.539068</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3433,20 +3981,30 @@
           <t>65167</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>-8.396380000000002</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-74.58132999999999</v>
-      </c>
-      <c r="I58" t="n">
-        <v>273</v>
-      </c>
-      <c r="J58" t="n">
-        <v>13</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-8.396380000000002</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-74.58133</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3485,20 +4043,30 @@
           <t>481 / 65100</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>-8.372491</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-74.541521</v>
-      </c>
-      <c r="I59" t="n">
-        <v>625</v>
-      </c>
-      <c r="J59" t="n">
-        <v>25</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-8.372491</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-74.541521</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -3537,20 +4105,30 @@
           <t>2 DE ABRIL / 65304 / 745</t>
         </is>
       </c>
-      <c r="G60" t="n">
-        <v>-8.41811</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-74.60473</v>
-      </c>
-      <c r="I60" t="n">
-        <v>637</v>
-      </c>
-      <c r="J60" t="n">
-        <v>26</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-8.41811</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-74.60473</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3589,20 +4167,30 @@
           <t>COLLEGE PREMIUM</t>
         </is>
       </c>
-      <c r="G61" t="n">
-        <v>-8.385277</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-74.543412</v>
-      </c>
-      <c r="I61" t="n">
-        <v>242</v>
-      </c>
-      <c r="J61" t="n">
-        <v>20</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-8.385277</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-74.543412</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/UCAYALI-CORONEL_PORTILLO-CALLERIA.xlsx
+++ b/ZonasEscolares/excels/UCAYALI-CORONEL_PORTILLO-CALLERIA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>251442</t>
+          <t>493238</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>64140</t>
+          <t>268</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-8.602410000000003</t>
+          <t>-8.388225</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-74.31007</t>
+          <t>-74.549952</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>202</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>493139</t>
+          <t>493766</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>232 NIÑO JESUS</t>
+          <t>435</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-8.380687</t>
+          <t>-8.410573</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-74.52893</t>
+          <t>-74.585102</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>243</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>493144</t>
+          <t>495100</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>235 SANTA ROSA</t>
+          <t>64871-B</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-8.387554</t>
+          <t>-8.36197</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-74.534025</t>
+          <t>-74.53072</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>204</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>493163</t>
+          <t>498839</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>JOAQUIN CAPELLO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-8.390618</t>
+          <t>-8.601812000000002</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-74.541539</t>
+          <t>-74.310901</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>224</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>493177</t>
+          <t>495464</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>242 DIVINO MAESTRO</t>
+          <t>COMERCIO 64</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-8.381146</t>
+          <t>-8.376641</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-74.54642</t>
+          <t>-74.53735</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>2246</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>101</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>493224</t>
+          <t>495280</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>261 VICTORIA BARCIA BONIFATI</t>
+          <t>65001 CORONEL PEDRO PORTILLO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-8.377184</t>
+          <t>-8.386566</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-74.537679</t>
+          <t>-74.53575</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>2579</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>102</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>493238</t>
+          <t>251442</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>64140</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-8.388225</t>
+          <t>-8.602410000000003</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-74.549952</t>
+          <t>-74.31007</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>221</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>493243</t>
+          <t>499075</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>269 ELVIRA GARCIA Y GARCIA</t>
+          <t>308 NIÑO JESUS DE PRAGA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-8.373144</t>
+          <t>-8.37692</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-74.551557</t>
+          <t>-74.55618</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>291</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>493257</t>
+          <t>493163</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>283 JUANA ALARCO DE DAMMERT</t>
+          <t>241</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-8.373603</t>
+          <t>-8.390618</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-74.529953</t>
+          <t>-74.541539</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>248</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>493766</t>
+          <t>813447</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>65167</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-8.410573</t>
+          <t>-8.396380000000002</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-74.585102</t>
+          <t>-74.58133</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>273</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>493785</t>
+          <t>493243</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>479 / 64001 / DANIEL ALCIDES CARRION</t>
+          <t>269 ELVIRA GARCIA Y GARCIA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-8.386652</t>
+          <t>-8.373144</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-74.5551</t>
+          <t>-74.551557</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>342</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>493790</t>
+          <t>499565</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>64004 MARGARITA A. AGUILAR A. / MARGARITA AURORA AGUILAR</t>
+          <t>64753 FAUSTINO MALDONADO</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-8.380832</t>
+          <t>-8.376569</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-74.543227</t>
+          <t>-74.557574</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>141</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>493808</t>
+          <t>493832</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>64005 FRANCISCO BOLOGNESI</t>
+          <t>64008 EL ORIENTE</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-8.393302</t>
+          <t>-8.378125000000002</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-74.541732</t>
+          <t>-74.546306</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>307</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>493813</t>
+          <t>493257</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>64006 JORGE CHAVEZ / JORGE CHAVEZ</t>
+          <t>283 JUANA ALARCO DE DAMMERT</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-8.384460000000002</t>
+          <t>-8.373603</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-74.541829</t>
+          <t>-74.529953</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1708</t>
+          <t>343</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>493827</t>
+          <t>647679</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>64007 SANTA ROSA</t>
+          <t>CRISTOBAL DE LOSADA Y PUGA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-8.389818</t>
+          <t>-8.382580000000003</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-74.530777</t>
+          <t>-74.53571</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>279</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>493832</t>
+          <t>548373</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>64008 EL ORIENTE</t>
+          <t>MARANATHA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-8.378125000000002</t>
+          <t>-8.39397</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-74.546306</t>
+          <t>-74.565892</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>284</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>493846</t>
+          <t>495968</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>64011 SOR ANNETA DE JESUS</t>
+          <t>BAUTISTA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-8.38029</t>
+          <t>-8.38054</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-74.52855</t>
+          <t>-74.5452</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1574</t>
+          <t>204</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>493851</t>
+          <t>499546</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>64012 MIGUEL GRAU</t>
+          <t>64693 JOSE OLAYA BALANDRA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-8.378917</t>
+          <t>-8.367884</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-74.534281</t>
+          <t>-74.548317</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>709</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>493865</t>
+          <t>826162</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>EL ARENAL</t>
+          <t>COLLEGE PREMIUM</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-8.374448</t>
+          <t>-8.385277</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-74.535181</t>
+          <t>-74.543412</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>242</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>493870</t>
+          <t>499985</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>64017</t>
+          <t>64087</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-8.374641</t>
+          <t>-8.310129</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-74.530629</t>
+          <t>-74.863785</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>466</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>493889</t>
+          <t>749866</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ABNER ALBERTO MONROY CACHAY</t>
+          <t>DON BOSCO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-8.370202000000003</t>
+          <t>-8.381627</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-74.53621</t>
+          <t>-74.539068</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>299</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>493894</t>
+          <t>495119</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>474 / 64020 LUIS ALBERTO SANCHEZ SANCHEZ</t>
+          <t>65297</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-8.373753000000002</t>
+          <t>-8.393483</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-74.551089</t>
+          <t>-74.567212</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>395</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>493907</t>
+          <t>493177</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>64023</t>
+          <t>242 DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-8.375804</t>
+          <t>-8.381146</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-74.543581</t>
+          <t>-74.54642</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>540</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>493912</t>
+          <t>493870</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>346 ROSA MERINO / 64024</t>
+          <t>64017</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-8.381145</t>
+          <t>-8.374641</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-74.536817</t>
+          <t>-74.530629</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>529</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>493974</t>
+          <t>495973</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>64035 AGROPECUARIO / COAR UCAYALI</t>
+          <t>UCAYALI</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-8.391996000000002</t>
+          <t>-8.383784</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-74.549076</t>
+          <t>-74.529542</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>353</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>493988</t>
+          <t>495992</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>64036</t>
+          <t>RICARDO PALMA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-8.393560000000003</t>
+          <t>-8.380342000000002</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-74.5373</t>
+          <t>-74.532862</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>207</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>494073</t>
+          <t>814022</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>64058 VICTOR MALDONADO BEGAZO / CRNL. VICTOR M. MALDONADO BEGAZO</t>
+          <t>481 / 65100</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-8.39533</t>
+          <t>-8.372491</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-74.58996</t>
+          <t>-74.541521</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2193</t>
+          <t>625</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>494488</t>
+          <t>493988</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>64359 JOSE GALVEZ EGUSQUIZA</t>
+          <t>64036</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-8.36726</t>
+          <t>-8.393560000000003</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-74.541893</t>
+          <t>-74.5373</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>571</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>494940</t>
+          <t>822258</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>64803</t>
+          <t>2 DE ABRIL / 65304 / 745</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-8.4116</t>
+          <t>-8.41811</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-74.5872</t>
+          <t>-74.60473</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>637</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>495100</t>
+          <t>639349</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>64871-B</t>
+          <t>65263 / FRANCISCO ODICIO ROMAN</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-8.36197</t>
+          <t>-8.414593</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-74.53072</t>
+          <t>-74.574027</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>640</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>495119</t>
+          <t>494488</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>65297</t>
+          <t>64359 JOSE GALVEZ EGUSQUIZA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-8.393483</t>
+          <t>-8.36726</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-74.567212</t>
+          <t>-74.541893</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>542</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>495280</t>
+          <t>493144</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>65001 CORONEL PEDRO PORTILLO</t>
+          <t>235 SANTA ROSA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-8.386566</t>
+          <t>-8.387554</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-74.53575</t>
+          <t>-74.534025</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2579</t>
+          <t>787</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>495299</t>
+          <t>691714</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>65002 AURISTELA DAVILA ZEVALLOS</t>
+          <t>65271</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-8.379614</t>
+          <t>-8.413007</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-74.539245</t>
+          <t>-74.646582</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>750</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>495303</t>
+          <t>493139</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>65003</t>
+          <t>232 NIÑO JESUS</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-8.3818</t>
+          <t>-8.380687</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-74.5311</t>
+          <t>-74.52893</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1749</t>
+          <t>775</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>495336</t>
+          <t>700105</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>65012 WILLIAN DYER AMPUDIA</t>
+          <t>ADUNI</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-8.394486000000002</t>
+          <t>-8.374537</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-74.571436</t>
+          <t>-74.537192</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>594</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>495459</t>
+          <t>493827</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>LA INMACULADA</t>
+          <t>64007 SANTA ROSA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-8.378601</t>
+          <t>-8.389818</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-74.531641</t>
+          <t>-74.530777</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>953</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>495464</t>
+          <t>493224</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>COMERCIO 64</t>
+          <t>261 VICTORIA BARCIA BONIFATI</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-8.376641</t>
+          <t>-8.377184</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-74.53735</t>
+          <t>-74.537679</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2246</t>
+          <t>803</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>495505</t>
+          <t>496005</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE GUADALUPE</t>
+          <t>ANTONIO RAYMONDI</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-8.381727</t>
+          <t>-8.38297</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-74.528421</t>
+          <t>-74.552165</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>406</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>495869</t>
+          <t>493894</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>474 / 64020 LUIS ALBERTO SANCHEZ SANCHEZ</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-8.406683</t>
+          <t>-8.373753000000002</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-74.569482</t>
+          <t>-74.551089</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>817</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>495968</t>
+          <t>493912</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>BAUTISTA</t>
+          <t>346 ROSA MERINO / 64024</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-8.38054</t>
+          <t>-8.381145</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-74.5452</t>
+          <t>-74.536817</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>860</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>495973</t>
+          <t>493808</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>UCAYALI</t>
+          <t>64005 FRANCISCO BOLOGNESI</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-8.383784</t>
+          <t>-8.393302</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-74.529542</t>
+          <t>-74.541732</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>803</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>495992</t>
+          <t>495336</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>RICARDO PALMA</t>
+          <t>65012 WILLIAN DYER AMPUDIA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-8.380342000000002</t>
+          <t>-8.394486000000002</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-74.532862</t>
+          <t>-74.571436</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>496005</t>
+          <t>493851</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ANTONIO RAYMONDI</t>
+          <t>64012 MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-8.38297</t>
+          <t>-8.378917</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-74.552165</t>
+          <t>-74.534281</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>498839</t>
+          <t>493889</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>JOAQUIN CAPELLO</t>
+          <t>ABNER ALBERTO MONROY CACHAY</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-8.601812000000002</t>
+          <t>-8.370202000000003</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-74.310901</t>
+          <t>-74.53621</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>499075</t>
+          <t>493790</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>308 NIÑO JESUS DE PRAGA</t>
+          <t>64004 MARGARITA A. AGUILAR A. / MARGARITA AURORA AGUILAR</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-8.37692</t>
+          <t>-8.380832</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-74.55618</t>
+          <t>-74.543227</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>499546</t>
+          <t>559192</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>64693 JOSE OLAYA BALANDRA</t>
+          <t>HUGO CRUZ DOZA</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-8.367884</t>
+          <t>-8.40771</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-74.548317</t>
+          <t>-74.59058</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>499565</t>
+          <t>493846</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>64753 FAUSTINO MALDONADO</t>
+          <t>64011 SOR ANNETA DE JESUS</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-8.376569</t>
+          <t>-8.38029</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-74.557574</t>
+          <t>-74.52855</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2795</t>
+          <t>1574</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>499985</t>
+          <t>493907</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>64087</t>
+          <t>64023</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-8.310129</t>
+          <t>-8.375804</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-74.863785</t>
+          <t>-74.543581</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>548373</t>
+          <t>494940</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MARANATHA</t>
+          <t>64803</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-8.39397</t>
+          <t>-8.4116</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-74.565892</t>
+          <t>-74.5872</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>559192</t>
+          <t>495505</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>HUGO CRUZ DOZA</t>
+          <t>NUESTRA SEÑORA DE GUADALUPE</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-8.40771</t>
+          <t>-8.381727</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-74.59058</t>
+          <t>-74.528421</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1353</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>639349</t>
+          <t>495303</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>65263 / FRANCISCO ODICIO ROMAN</t>
+          <t>65003</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-8.414593</t>
+          <t>-8.3818</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-74.574027</t>
+          <t>-74.5311</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>1749</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>67</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>647679</t>
+          <t>493785</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CRISTOBAL DE LOSADA Y PUGA</t>
+          <t>479 / 64001 / DANIEL ALCIDES CARRION</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-8.382580000000003</t>
+          <t>-8.386652</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-74.53571</t>
+          <t>-74.5551</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>691714</t>
+          <t>495299</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>65271</t>
+          <t>65002 AURISTELA DAVILA ZEVALLOS</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-8.413007</t>
+          <t>-8.379614</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-74.646582</t>
+          <t>-74.539245</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>1942</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>700105</t>
+          <t>493974</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>ADUNI</t>
+          <t>64035 AGROPECUARIO / COAR UCAYALI</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-8.374537</t>
+          <t>-8.391996000000002</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-74.537192</t>
+          <t>-74.549076</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>76</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>749866</t>
+          <t>493813</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>DON BOSCO</t>
+          <t>64006 JORGE CHAVEZ / JORGE CHAVEZ</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-8.381627</t>
+          <t>-8.384460000000002</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-74.539068</t>
+          <t>-74.541829</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>1708</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>80</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>813447</t>
+          <t>493865</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>65167</t>
+          <t>EL ARENAL</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-8.396380000000002</t>
+          <t>-8.374448</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-74.58133</t>
+          <t>-74.535181</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>87</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>814022</t>
+          <t>494073</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>481 / 65100</t>
+          <t>64058 VICTOR MALDONADO BEGAZO / CRNL. VICTOR M. MALDONADO BEGAZO</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-8.372491</t>
+          <t>-8.39533</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-74.541521</t>
+          <t>-74.58996</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>2193</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>89</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>822258</t>
+          <t>495869</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2 DE ABRIL / 65304 / 745</t>
+          <t>289</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-8.41811</t>
+          <t>-8.406683</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-74.60473</t>
+          <t>-74.569482</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>201</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>826162</t>
+          <t>495459</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>COLLEGE PREMIUM</t>
+          <t>LA INMACULADA</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-8.385277</t>
+          <t>-8.378601</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-74.543412</t>
+          <t>-74.531641</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>98</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">

--- a/ZonasEscolares/excels/UCAYALI-CORONEL_PORTILLO-CALLERIA.xlsx
+++ b/ZonasEscolares/excels/UCAYALI-CORONEL_PORTILLO-CALLERIA.xlsx
@@ -697,7 +697,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-8.601812000000002</t>
+          <t>-8.601812</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-8.602410000000003</t>
+          <t>-8.60241</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-8.384315000000003</t>
+          <t>-8.384315</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-8.396380000000002</t>
+          <t>-8.39638</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-8.378125000000002</t>
+          <t>-8.378125</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-8.382580000000003</t>
+          <t>-8.38258</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-8.380342000000002</t>
+          <t>-8.380342</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-8.393560000000003</t>
+          <t>-8.39356</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-8.373753000000002</t>
+          <t>-8.373753</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-8.394486000000002</t>
+          <t>-8.394486</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-8.370202000000003</t>
+          <t>-8.370202</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-8.391996000000002</t>
+          <t>-8.391996</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-8.384460000000002</t>
+          <t>-8.38446</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">

--- a/ZonasEscolares/excels/UCAYALI-CORONEL_PORTILLO-CALLERIA.xlsx
+++ b/ZonasEscolares/excels/UCAYALI-CORONEL_PORTILLO-CALLERIA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>493238</t>
+          <t>826162</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>COLLEGE PREMIUM</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-8.388225</t>
+          <t>242</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-74.549952</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>-8.385277</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-74.543412</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>493766</t>
+          <t>822258</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>2 DE ABRIL / 65304 / 745</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-8.410573</t>
+          <t>637</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-74.585102</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>-8.41811</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-74.60473</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>495100</t>
+          <t>814022</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>64871-B</t>
+          <t>481 / 65100</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-8.36197</t>
+          <t>625</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-74.53072</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>-8.372491</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-74.541521</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>498839</t>
+          <t>813447</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>JOAQUIN CAPELLO</t>
+          <t>65167</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-8.601812</t>
+          <t>273</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-74.310901</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>-8.396380000000002</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-74.58133</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>495464</t>
+          <t>749866</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>COMERCIO 64</t>
+          <t>DON BOSCO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-8.376641</t>
+          <t>299</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-74.53735</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2246</t>
+          <t>-8.381627</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>-74.539068</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>495280</t>
+          <t>700105</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>65001 CORONEL PEDRO PORTILLO</t>
+          <t>ADUNI</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-8.386566</t>
+          <t>594</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-74.53575</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2579</t>
+          <t>-8.374537</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>-74.537192</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>251442</t>
+          <t>691714</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>64140</t>
+          <t>65271</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-8.60241</t>
+          <t>750</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-74.31007</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>-8.413007</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-74.646582</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>499075</t>
+          <t>647679</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>308 NIÑO JESUS DE PRAGA</t>
+          <t>CRISTOBAL DE LOSADA Y PUGA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-8.37692</t>
+          <t>279</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-74.55618</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>-8.382580000000003</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-74.53571</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>493163</t>
+          <t>639349</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>65263 / FRANCISCO ODICIO ROMAN</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-8.390618</t>
+          <t>640</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-74.541539</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>-8.414593</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-74.574027</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>493356</t>
+          <t>559192</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>311 SOR ANGELA CATELLI CATELLI</t>
+          <t>HUGO CRUZ DOZA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-8.384315</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-74.542465</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>-8.40771</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-74.59058</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>813447</t>
+          <t>548373</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>65167</t>
+          <t>MARANATHA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-8.39638</t>
+          <t>284</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-74.58133</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>-8.39397</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-74.565892</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>493243</t>
+          <t>499985</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>269 ELVIRA GARCIA Y GARCIA</t>
+          <t>64087</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-8.373144</t>
+          <t>466</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-74.551557</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>-8.310129</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-74.863785</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1255,22 +1255,22 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>2795</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>-8.376569</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>-74.557574</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2795</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>141</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>493832</t>
+          <t>499546</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>64008 EL ORIENTE</t>
+          <t>64693 JOSE OLAYA BALANDRA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-8.378125</t>
+          <t>709</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-74.546306</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>-8.367884</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-74.548317</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>493257</t>
+          <t>499075</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>283 JUANA ALARCO DE DAMMERT</t>
+          <t>308 NIÑO JESUS DE PRAGA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-8.373603</t>
+          <t>291</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-74.529953</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>-8.37692</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-74.55618</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>647679</t>
+          <t>498839</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CRISTOBAL DE LOSADA Y PUGA</t>
+          <t>JOAQUIN CAPELLO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-8.38258</t>
+          <t>224</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-74.53571</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>-8.601812000000002</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-74.310901</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>548373</t>
+          <t>496005</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MARANATHA</t>
+          <t>ANTONIO RAYMONDI</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-8.39397</t>
+          <t>406</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-74.565892</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>-8.38297</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-74.552165</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>495968</t>
+          <t>495992</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>BAUTISTA</t>
+          <t>RICARDO PALMA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-8.38054</t>
+          <t>207</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-74.5452</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>-8.380342000000002</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-74.532862</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>499546</t>
+          <t>495973</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>64693 JOSE OLAYA BALANDRA</t>
+          <t>UCAYALI</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-8.367884</t>
+          <t>353</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-74.548317</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>-8.383784</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-74.529542</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>826162</t>
+          <t>495968</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>COLLEGE PREMIUM</t>
+          <t>BAUTISTA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-8.385277</t>
+          <t>204</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-74.543412</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>-8.38054</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-74.5452</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>499985</t>
+          <t>495869</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>64087</t>
+          <t>289</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-8.310129</t>
+          <t>201</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-74.863785</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>-8.406683</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-74.569482</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>749866</t>
+          <t>495505</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>DON BOSCO</t>
+          <t>NUESTRA SEÑORA DE GUADALUPE</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-8.381627</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-74.539068</t>
+          <t>61</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>-8.381727</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-74.528421</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>495119</t>
+          <t>495464</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>65297</t>
+          <t>COMERCIO 64</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-8.393483</t>
+          <t>2246</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-74.567212</t>
+          <t>101</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>-8.376641</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-74.53735</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>493177</t>
+          <t>495459</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>242 DIVINO MAESTRO</t>
+          <t>LA INMACULADA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-8.381146</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-74.54642</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>-8.378601</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-74.531641</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>493870</t>
+          <t>495336</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>64017</t>
+          <t>65012 WILLIAN DYER AMPUDIA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-8.374641</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-74.530629</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>-8.394486000000002</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-74.571436</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>495973</t>
+          <t>495303</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UCAYALI</t>
+          <t>65003</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-8.383784</t>
+          <t>1749</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-74.529542</t>
+          <t>67</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>-8.3818</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-74.5311</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>495992</t>
+          <t>495299</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>RICARDO PALMA</t>
+          <t>65002 AURISTELA DAVILA ZEVALLOS</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-8.380342</t>
+          <t>1942</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-74.532862</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>-8.379614</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-74.539245</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>814022</t>
+          <t>495280</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>481 / 65100</t>
+          <t>65001 CORONEL PEDRO PORTILLO</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-8.372491</t>
+          <t>2579</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-74.541521</t>
+          <t>102</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>-8.386566</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-74.53575</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>493988</t>
+          <t>495119</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>64036</t>
+          <t>65297</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-8.39356</t>
+          <t>395</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-74.5373</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>-8.393483</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-74.567212</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>822258</t>
+          <t>495100</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2 DE ABRIL / 65304 / 745</t>
+          <t>64871-B</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-8.41811</t>
+          <t>204</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-74.60473</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>-8.36197</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-74.53072</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>639349</t>
+          <t>494940</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>65263 / FRANCISCO ODICIO ROMAN</t>
+          <t>64803</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-8.414593</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-74.574027</t>
+          <t>61</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>-8.4116</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-74.5872</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2433,22 +2433,22 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
+          <t>542</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
           <t>-8.36726</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>-74.541893</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>542</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>28</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>493144</t>
+          <t>494073</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>235 SANTA ROSA</t>
+          <t>64058 VICTOR MALDONADO BEGAZO / CRNL. VICTOR M. MALDONADO BEGAZO</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-8.387554</t>
+          <t>2193</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-74.534025</t>
+          <t>89</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>-8.39533</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-74.58996</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>691714</t>
+          <t>493988</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>65271</t>
+          <t>64036</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-8.413007</t>
+          <t>571</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-74.646582</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>-8.393560000000003</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-74.5373</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>493139</t>
+          <t>493974</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>232 NIÑO JESUS</t>
+          <t>64035 AGROPECUARIO / COAR UCAYALI</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-8.380687</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-74.52893</t>
+          <t>76</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>-8.391996000000002</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-74.549076</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>700105</t>
+          <t>493912</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ADUNI</t>
+          <t>346 ROSA MERINO / 64024</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-8.374537</t>
+          <t>860</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-74.537192</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>-8.381145</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-74.536817</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>493827</t>
+          <t>493907</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>64007 SANTA ROSA</t>
+          <t>64023</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-8.389818</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-74.530777</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>-8.375804</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-74.543581</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>493224</t>
+          <t>493894</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>261 VICTORIA BARCIA BONIFATI</t>
+          <t>474 / 64020 LUIS ALBERTO SANCHEZ SANCHEZ</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-8.377184</t>
+          <t>817</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-74.537679</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>-8.373753000000002</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-74.551089</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>496005</t>
+          <t>493889</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ANTONIO RAYMONDI</t>
+          <t>ABNER ALBERTO MONROY CACHAY</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-8.38297</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-74.552165</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>-8.370202000000003</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-74.53621</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>493894</t>
+          <t>493870</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>474 / 64020 LUIS ALBERTO SANCHEZ SANCHEZ</t>
+          <t>64017</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-8.373753</t>
+          <t>529</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-74.551089</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>-8.374641</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-74.530629</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>493912</t>
+          <t>493865</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>346 ROSA MERINO / 64024</t>
+          <t>EL ARENAL</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-8.381145</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-74.536817</t>
+          <t>87</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>-8.374448</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-74.535181</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>493808</t>
+          <t>493851</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>64005 FRANCISCO BOLOGNESI</t>
+          <t>64012 MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-8.393302</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-74.541732</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>-8.378917</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-74.534281</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>495336</t>
+          <t>493846</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>65012 WILLIAN DYER AMPUDIA</t>
+          <t>64011 SOR ANNETA DE JESUS</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-8.394486</t>
+          <t>1574</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-74.571436</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>-8.38029</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>-74.52855</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>493851</t>
+          <t>493832</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>64012 MIGUEL GRAU</t>
+          <t>64008 EL ORIENTE</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-8.378917</t>
+          <t>307</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-74.534281</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>-8.378125000000002</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-74.546306</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>493889</t>
+          <t>493827</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ABNER ALBERTO MONROY CACHAY</t>
+          <t>64007 SANTA ROSA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-8.370202</t>
+          <t>953</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-74.53621</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>-8.389818</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>-74.530777</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>493790</t>
+          <t>493813</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>64004 MARGARITA A. AGUILAR A. / MARGARITA AURORA AGUILAR</t>
+          <t>64006 JORGE CHAVEZ / JORGE CHAVEZ</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-8.380832</t>
+          <t>1708</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-74.543227</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>-8.384460000000002</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>-74.541829</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>559192</t>
+          <t>493808</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>HUGO CRUZ DOZA</t>
+          <t>64005 FRANCISCO BOLOGNESI</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-8.40771</t>
+          <t>803</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-74.59058</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1353</t>
+          <t>-8.393302</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>-74.541732</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>493846</t>
+          <t>493790</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>64011 SOR ANNETA DE JESUS</t>
+          <t>64004 MARGARITA A. AGUILAR A. / MARGARITA AURORA AGUILAR</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-8.38029</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-74.52855</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1574</t>
+          <t>-8.380832</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>-74.543227</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>493907</t>
+          <t>493785</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>64023</t>
+          <t>479 / 64001 / DANIEL ALCIDES CARRION</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-8.375804</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-74.543581</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>-8.386652</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>-74.5551</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>494940</t>
+          <t>493766</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>64803</t>
+          <t>435</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-8.4116</t>
+          <t>243</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-74.5872</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>-8.410573</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>-74.585102</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>495505</t>
+          <t>493356</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE GUADALUPE</t>
+          <t>311 SOR ANGELA CATELLI CATELLI</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-8.381727</t>
+          <t>347</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-74.528421</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>-8.384315000000003</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>-74.542465</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>495303</t>
+          <t>493257</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>65003</t>
+          <t>283 JUANA ALARCO DE DAMMERT</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-8.3818</t>
+          <t>343</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-74.5311</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1749</t>
+          <t>-8.373603</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>-74.529953</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>493785</t>
+          <t>493243</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>479 / 64001 / DANIEL ALCIDES CARRION</t>
+          <t>269 ELVIRA GARCIA Y GARCIA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-8.386652</t>
+          <t>342</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-74.5551</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>-8.373144</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>-74.551557</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>495299</t>
+          <t>493238</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>65002 AURISTELA DAVILA ZEVALLOS</t>
+          <t>268</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-8.379614</t>
+          <t>202</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-74.539245</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>-8.388225</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>-74.549952</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>493974</t>
+          <t>493224</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>64035 AGROPECUARIO / COAR UCAYALI</t>
+          <t>261 VICTORIA BARCIA BONIFATI</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-8.391996</t>
+          <t>803</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-74.549076</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>-8.377184</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>-74.537679</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>493813</t>
+          <t>493177</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>64006 JORGE CHAVEZ / JORGE CHAVEZ</t>
+          <t>242 DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-8.38446</t>
+          <t>540</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-74.541829</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1708</t>
+          <t>-8.381146</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>-74.54642</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>493865</t>
+          <t>493163</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>EL ARENAL</t>
+          <t>241</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-8.374448</t>
+          <t>248</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-74.535181</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>-8.390618</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>-74.541539</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>494073</t>
+          <t>493144</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>64058 VICTOR MALDONADO BEGAZO / CRNL. VICTOR M. MALDONADO BEGAZO</t>
+          <t>235 SANTA ROSA</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-8.39533</t>
+          <t>787</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-74.58996</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2193</t>
+          <t>-8.387554</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>-74.534025</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>495869</t>
+          <t>493139</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>232 NIÑO JESUS</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-8.406683</t>
+          <t>775</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-74.569482</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>-8.380687</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-74.52893</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>495459</t>
+          <t>251442</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>LA INMACULADA</t>
+          <t>64140</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-8.378601</t>
+          <t>221</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-74.531641</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>-8.602410000000003</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>-74.31007</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">

--- a/ZonasEscolares/excels/UCAYALI-CORONEL_PORTILLO-CALLERIA.xlsx
+++ b/ZonasEscolares/excels/UCAYALI-CORONEL_PORTILLO-CALLERIA.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
